--- a/output/pdf_financials_xlsx/FL.xlsx
+++ b/output/pdf_financials_xlsx/FL.xlsx
@@ -5985,10 +5985,10 @@
         <v>32.312</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>31.853</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>33.659</v>
       </c>
     </row>
     <row r="93">
@@ -10233,7 +10233,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FL.xlsx
+++ b/output/pdf_financials_xlsx/FL.xlsx
@@ -1068,16 +1068,16 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.622</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.918</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-1.038</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.349</v>
       </c>
     </row>
     <row r="13">
@@ -2020,16 +2020,16 @@
         <v>-10.951</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-24.232</v>
+        <v>-23.61</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-24.526</v>
+        <v>-23.608</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-20.485</v>
+        <v>-19.447</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-11.185</v>
+        <v>-10.836</v>
       </c>
     </row>
     <row r="28">
@@ -2136,16 +2136,16 @@
         <v>-10.846</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-23.901</v>
+        <v>-23.279</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-24.12</v>
+        <v>-23.202</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-19.833</v>
+        <v>-18.795</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-10.384</v>
+        <v>-10.035</v>
       </c>
     </row>
     <row r="30">
@@ -33735,7 +33735,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -33836,7 +33836,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -35131,7 +35131,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -35747,7 +35747,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">

--- a/output/pdf_financials_xlsx/FL.xlsx
+++ b/output/pdf_financials_xlsx/FL.xlsx
@@ -1294,10 +1294,10 @@
         <v>-1.819026</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-8.233000000000001</v>
+        <v>-8.071999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-10.951</v>
+        <v>-10.566</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-24.232</v>
@@ -1352,10 +1352,10 @@
         <v>0.172515</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.161</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.385</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0</v>
@@ -2014,10 +2014,10 @@
         <v>-1.819026</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-8.233000000000001</v>
+        <v>-8.071999999999999</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-10.951</v>
+        <v>-10.566</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-23.61</v>
@@ -2130,10 +2130,10 @@
         <v>-1.819026</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-8.148</v>
+        <v>-7.987</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-10.846</v>
+        <v>-10.461</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-23.279</v>
@@ -2280,10 +2280,10 @@
         <v>-9.483921615194065</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.994549058473736</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.643763013439334</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
@@ -4603,22 +4603,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="71">
@@ -4661,22 +4661,22 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="72">
@@ -4893,22 +4893,22 @@
         <v>0.121</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>7.547</v>
+        <v>7.489</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>31.721</v>
+        <v>31.575</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>33.565</v>
+        <v>33.408</v>
       </c>
     </row>
     <row r="76">
@@ -5087,22 +5087,22 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>1.999</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="79">
@@ -5145,22 +5145,22 @@
         <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>0</v>
+        <v>1.999</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="80">
@@ -5224,35 +5224,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.003138485680659082</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.004631615061326014</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.003610108303249098</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.004661675377878231</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>-0.5159971133028627</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>-0.1595880568417691</v>
       </c>
     </row>
     <row r="81">
@@ -5527,22 +5515,22 @@
         <v>0</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.066</v>
+        <v>0.04</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>5.367</v>
+        <v>3.368</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6431,10 +6419,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.005065</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.023249</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0.044976</v>
@@ -6461,7 +6449,7 @@
         <v>-0.006556</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>-0.016</v>
+        <v>-0.102496</v>
       </c>
       <c r="M101" s="3" t="n">
         <v>0</v>
@@ -7059,7 +7047,7 @@
         <v>-3.91</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="112">
@@ -8451,7 +8439,7 @@
         <v>-3.91</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="135">
@@ -9358,7 +9346,11 @@
           <t>Current portion of lease obligations 6</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -9851,7 +9843,11 @@
           <t>Lease obligations 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11011,7 +11007,11 @@
           <t>Current portion of lease obligations 7</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11306,7 +11306,11 @@
           <t>Lease obligations 7</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -12001,7 +12005,11 @@
           <t>Current portion of lease obligations 8</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12098,7 +12106,11 @@
           <t>Lease obligations 8</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -20637,7 +20649,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -25510,7 +25526,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -28141,7 +28161,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -30511,7 +30535,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -32743,7 +32771,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E248" s="5" t="n">
         <v>-0.25751</v>
       </c>
@@ -33042,7 +33074,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E251" s="5" t="n">
         <v>0.005065</v>
       </c>
@@ -36551,7 +36587,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -37155,7 +37195,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
